--- a/Project.xlsx
+++ b/Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbb979f32a3cc8c2/Desktop/Coding Projects/CPCS 3620 - Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BEB67EB-998E-491F-BF4C-05ED7FFF8C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{2BEB67EB-998E-491F-BF4C-05ED7FFF8C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCCB6200-FC00-4798-AE90-E9F02B0E3CF4}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{9909C254-231F-494F-836C-6F74D18885DB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Task Name</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Project - PSYC 2005</t>
+  </si>
+  <si>
+    <t>Play Valorant</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C869AF-D1C6-4434-8532-A1A2913DD867}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="16.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -598,6 +601,20 @@
         <v>50</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -605,23 +622,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010035DEED250034E14C8F9587FA15482C6E" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="91acee58b8e57114428d0280b7eaa2b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d8a71fe4b0265b65a74a6259a40a5d9" ns3:_="">
     <xsd:import namespace="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
@@ -777,31 +777,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254D1D5B-753A-4C95-96D5-0CD8C5AC28ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67AF191C-6CC6-400C-B89E-F033E1598B44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2E69CF0-E000-48A8-9029-CB726ED53C4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -817,4 +810,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67AF191C-6CC6-400C-B89E-F033E1598B44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254D1D5B-753A-4C95-96D5-0CD8C5AC28ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Project.xlsx
+++ b/Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbb979f32a3cc8c2/Desktop/Coding Projects/CPCS 3620 - Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{2BEB67EB-998E-491F-BF4C-05ED7FFF8C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCCB6200-FC00-4798-AE90-E9F02B0E3CF4}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{2BEB67EB-998E-491F-BF4C-05ED7FFF8C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{315D2DCC-E16A-4A18-81C1-987212D9AE2C}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{9909C254-231F-494F-836C-6F74D18885DB}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1512" windowWidth="17280" windowHeight="8880" xr2:uid="{9909C254-231F-494F-836C-6F74D18885DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,6 +149,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +498,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -522,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
@@ -536,7 +540,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3">
         <v>7</v>
@@ -550,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3">
         <v>9</v>
@@ -578,7 +582,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3">
         <v>6</v>
@@ -606,22 +610,47 @@
         <v>12</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>60</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations xWindow="676" yWindow="308" count="5">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Out of Scale" error="The value you have is out of scale (Valid: 1 - 10)" promptTitle="Importance Scale" prompt="Please enter the level of importance from 1 to 10." sqref="B1:B1048576" xr:uid="{E3012157-0E28-4199-9754-70DC151FC5AA}">
+      <formula1>1</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Time" error="you cannot have the deadline today, please do them right now" promptTitle="Days until deadline" prompt="Please enter the days before the deadline, IMPORTANT: Will not accept if today is the deadline" sqref="C1 C3:C1048576" xr:uid="{5220F806-13FF-4CF9-862A-0FA8CDBD5381}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Time" error="you cannot have the deadline today, please do them right now or deadline has passed." promptTitle="Days until deadline" prompt="Please enter the days before the deadline, IMPORTANT: Will not accept if today is the deadline" sqref="C2" xr:uid="{A44A15CD-22DF-4B4E-85AC-222EB88FB0E6}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Estimated Minutes" prompt="Please enter the estimated time that you will take to finsih this task in minutes." sqref="D1:D1048576" xr:uid="{DF51144E-24A4-495A-930F-94C1A47E9E3C}">
+      <formula1>0</formula1>
+      <formula2>360</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Task Name" prompt="Please enter the name of your task." sqref="A1:A1048576" xr:uid="{EBDC28AF-5132-4901-9FA9-F58911EFB690}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010035DEED250034E14C8F9587FA15482C6E" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="91acee58b8e57114428d0280b7eaa2b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d8a71fe4b0265b65a74a6259a40a5d9" ns3:_="">
     <xsd:import namespace="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
@@ -777,7 +806,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -786,15 +815,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bedfe06a-2c95-41f5-9b7a-540a0127f0b4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254D1D5B-753A-4C95-96D5-0CD8C5AC28ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2E69CF0-E000-48A8-9029-CB726ED53C4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -812,26 +849,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67AF191C-6CC6-400C-B89E-F033E1598B44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254D1D5B-753A-4C95-96D5-0CD8C5AC28ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="bedfe06a-2c95-41f5-9b7a-540a0127f0b4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>